--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-10-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.98</t>
+          <t>£9.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.89</t>
+          <t>£20.82</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.48</t>
+          <t>£25.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£33.30</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.59</t>
+          <t>£38.48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£28.43</t>
+          <t>£28.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>£30.00</t>
+          <t>£28.13 Pre Sale Price-£30.00</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£34.64</t>
+          <t>£34.29</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>£35.83</t>
+          <t>£33.96 Pre Sale Price-£35.83</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£37.42</t>
+          <t>£37.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>£40.83</t>
+          <t>£36.86 Pre Sale Price-£40.83</t>
         </is>
       </c>
     </row>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>£45.83</t>
+          <t>£42.03 Pre Sale Price-£45.83</t>
         </is>
       </c>
     </row>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff74f70e8e5+80021]
-	GetHandleVerifier [0x0x7ff74f70e940+80112]
-	(No symbol) [0x0x7ff74f49060f]
-	(No symbol) [0x0x7ff74f4e8854]
-	(No symbol) [0x0x7ff74f4e8b1c]
-	(No symbol) [0x0x7ff74f53c927]
-	(No symbol) [0x0x7ff74f51126f]
-	(No symbol) [0x0x7ff74f53968a]
-	(No symbol) [0x0x7ff74f511003]
-	(No symbol) [0x0x7ff74f4d95d1]
-	(No symbol) [0x0x7ff74f4da3f3]
-	GetHandleVerifier [0x0x7ff74f9cdc7d+2960429]
-	GetHandleVerifier [0x0x7ff74f9c7f3a+2936554]
-	GetHandleVerifier [0x0x7ff74f9e8977+3070247]
-	GetHandleVerifier [0x0x7ff74f7283ce+185214]
-	GetHandleVerifier [0x0x7ff74f72fe1f+216527]
-	GetHandleVerifier [0x0x7ff74f717b24+117460]
-	GetHandleVerifier [0x0x7ff74f717cdf+117903]
-	GetHandleVerifier [0x0x7ff74f6fdbb8+11112]
+	GetHandleVerifier [0x0x7ff6d507e8e5+80021]
+	GetHandleVerifier [0x0x7ff6d507e940+80112]
+	(No symbol) [0x0x7ff6d4e0060f]
+	(No symbol) [0x0x7ff6d4e58854]
+	(No symbol) [0x0x7ff6d4e58b1c]
+	(No symbol) [0x0x7ff6d4eac927]
+	(No symbol) [0x0x7ff6d4e8126f]
+	(No symbol) [0x0x7ff6d4ea968a]
+	(No symbol) [0x0x7ff6d4e81003]
+	(No symbol) [0x0x7ff6d4e495d1]
+	(No symbol) [0x0x7ff6d4e4a3f3]
+	GetHandleVerifier [0x0x7ff6d533dc7d+2960429]
+	GetHandleVerifier [0x0x7ff6d5337f3a+2936554]
+	GetHandleVerifier [0x0x7ff6d5358977+3070247]
+	GetHandleVerifier [0x0x7ff6d50983ce+185214]
+	GetHandleVerifier [0x0x7ff6d509fe1f+216527]
+	GetHandleVerifier [0x0x7ff6d5087b24+117460]
+	GetHandleVerifier [0x0x7ff6d5087cdf+117903]
+	GetHandleVerifier [0x0x7ff6d506dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
